--- a/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\TaskMgmt_FloorPlan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EFF0F8-10DF-4E44-B8A7-847ADAE63EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9AEA2-C4D4-4D34-B55C-67182E3B47E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C0C90F87-48CD-475A-8923-C466A25A0B95}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{C0C90F87-48CD-475A-8923-C466A25A0B95}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="320">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login as User A with valid credentials</t>
@@ -1458,25 +1455,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1484,13 +1478,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,16 +1492,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1515,13 +1509,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1529,19 +1523,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1549,13 +1543,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1563,16 +1557,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1580,13 +1574,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1594,19 +1588,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" t="s">
         <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1614,16 +1608,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1631,13 +1625,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1645,22 +1639,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
         <v>39</v>
       </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>41</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>43</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -1671,16 +1665,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1688,13 +1682,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1702,16 +1696,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>49</v>
-      </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1719,13 +1713,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1733,19 +1727,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
         <v>51</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>52</v>
       </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1753,13 +1747,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
         <v>54</v>
       </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1767,13 +1761,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" t="s">
         <v>56</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" t="s">
         <v>57</v>
-      </c>
-      <c r="J21" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1781,19 +1775,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
         <v>59</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>60</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>61</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" t="s">
         <v>62</v>
-      </c>
-      <c r="J22" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1801,16 +1795,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="C23" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>65</v>
-      </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1818,13 +1812,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1832,16 +1826,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>68</v>
       </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1849,13 +1843,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1863,19 +1857,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
         <v>71</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>72</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" t="s">
         <v>73</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="K27" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1883,19 +1877,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" t="s">
         <v>75</v>
       </c>
-      <c r="C28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" t="s">
         <v>76</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="K28" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1903,19 +1897,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
         <v>78</v>
       </c>
-      <c r="C29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" t="s">
+      <c r="K29" t="s">
         <v>80</v>
-      </c>
-      <c r="K29" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1923,16 +1917,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" t="s">
         <v>82</v>
       </c>
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" t="s">
-        <v>83</v>
-      </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1940,13 +1934,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1954,16 +1948,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
         <v>85</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>86</v>
       </c>
-      <c r="D32" t="s">
-        <v>87</v>
-      </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1971,13 +1965,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
         <v>88</v>
       </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1985,19 +1979,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" t="s">
         <v>90</v>
       </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
+        <v>79</v>
+      </c>
+      <c r="K34" t="s">
         <v>91</v>
-      </c>
-      <c r="F34" t="s">
-        <v>80</v>
-      </c>
-      <c r="K34" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2005,19 +1999,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" t="s">
         <v>93</v>
       </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" t="s">
         <v>94</v>
-      </c>
-      <c r="F35" t="s">
-        <v>80</v>
-      </c>
-      <c r="K35" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2025,19 +2019,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
         <v>96</v>
       </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>79</v>
+      </c>
+      <c r="K36" t="s">
         <v>97</v>
-      </c>
-      <c r="F36" t="s">
-        <v>80</v>
-      </c>
-      <c r="K36" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2045,19 +2039,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" t="s">
         <v>99</v>
       </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
+        <v>79</v>
+      </c>
+      <c r="K37" t="s">
         <v>100</v>
-      </c>
-      <c r="F37" t="s">
-        <v>80</v>
-      </c>
-      <c r="K37" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2065,16 +2059,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
         <v>102</v>
       </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2082,13 +2076,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2096,16 +2090,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2113,13 +2107,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2127,19 +2121,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" t="s">
         <v>107</v>
       </c>
-      <c r="C42" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" t="s">
-        <v>108</v>
-      </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2147,13 +2141,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
         <v>109</v>
       </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2161,19 +2155,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" t="s">
         <v>111</v>
       </c>
-      <c r="C44" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
+        <v>79</v>
+      </c>
+      <c r="K44" t="s">
         <v>112</v>
-      </c>
-      <c r="F44" t="s">
-        <v>80</v>
-      </c>
-      <c r="K44" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2181,19 +2175,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" t="s">
         <v>114</v>
       </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
+        <v>79</v>
+      </c>
+      <c r="K45" t="s">
         <v>115</v>
-      </c>
-      <c r="F45" t="s">
-        <v>80</v>
-      </c>
-      <c r="K45" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2201,19 +2195,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
         <v>117</v>
       </c>
-      <c r="C46" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="F46" t="s">
+        <v>79</v>
+      </c>
+      <c r="K46" t="s">
         <v>118</v>
-      </c>
-      <c r="F46" t="s">
-        <v>80</v>
-      </c>
-      <c r="K46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2221,16 +2215,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" t="s">
         <v>120</v>
       </c>
-      <c r="C47" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" t="s">
-        <v>121</v>
-      </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2238,13 +2232,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2252,16 +2246,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -2269,13 +2263,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -2283,16 +2277,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" t="s">
         <v>125</v>
       </c>
-      <c r="C51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" t="s">
-        <v>126</v>
-      </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2300,13 +2294,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s">
         <v>127</v>
       </c>
-      <c r="C52" t="s">
-        <v>128</v>
-      </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2314,16 +2308,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" t="s">
         <v>129</v>
       </c>
-      <c r="C53" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
       <c r="F53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2331,13 +2325,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2345,16 +2339,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" t="s">
         <v>132</v>
       </c>
-      <c r="C55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" t="s">
-        <v>133</v>
-      </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2362,16 +2356,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" t="s">
         <v>134</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>135</v>
       </c>
-      <c r="D56" t="s">
-        <v>136</v>
-      </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2379,13 +2373,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2393,19 +2387,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" t="s">
         <v>138</v>
       </c>
-      <c r="C58" t="s">
-        <v>135</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="F58" t="s">
+        <v>79</v>
+      </c>
+      <c r="K58" t="s">
         <v>139</v>
-      </c>
-      <c r="F58" t="s">
-        <v>80</v>
-      </c>
-      <c r="K58" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2413,16 +2407,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" t="s">
         <v>141</v>
       </c>
-      <c r="C59" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" t="s">
-        <v>142</v>
-      </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2430,13 +2424,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" t="s">
         <v>143</v>
       </c>
-      <c r="C60" t="s">
-        <v>144</v>
-      </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2444,16 +2438,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" t="s">
         <v>145</v>
       </c>
-      <c r="C61" t="s">
-        <v>144</v>
-      </c>
-      <c r="D61" t="s">
-        <v>146</v>
-      </c>
       <c r="F61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2461,13 +2455,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" t="s">
         <v>147</v>
       </c>
-      <c r="C62" t="s">
-        <v>148</v>
-      </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2475,19 +2469,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" t="s">
         <v>149</v>
       </c>
-      <c r="C63" t="s">
-        <v>148</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63" t="s">
         <v>150</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-      <c r="K63" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2495,16 +2489,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" t="s">
         <v>152</v>
       </c>
-      <c r="C64" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64" t="s">
-        <v>153</v>
-      </c>
       <c r="F64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2512,13 +2506,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -2526,16 +2520,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" t="s">
         <v>155</v>
       </c>
-      <c r="C66" t="s">
-        <v>148</v>
-      </c>
-      <c r="D66" t="s">
-        <v>156</v>
-      </c>
       <c r="F66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -2543,13 +2537,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2557,16 +2551,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" t="s">
         <v>158</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>159</v>
       </c>
-      <c r="D68" t="s">
-        <v>160</v>
-      </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2574,13 +2568,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2588,16 +2582,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" t="s">
         <v>162</v>
       </c>
-      <c r="C70" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" t="s">
-        <v>163</v>
-      </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2605,16 +2599,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" t="s">
         <v>164</v>
       </c>
-      <c r="C71" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" t="s">
-        <v>165</v>
-      </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -2622,10 +2616,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>165</v>
+      </c>
+      <c r="F72" t="s">
         <v>166</v>
-      </c>
-      <c r="F72" t="s">
-        <v>167</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -2636,16 +2630,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
         <v>168</v>
-      </c>
-      <c r="C73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2653,13 +2647,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2667,16 +2661,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" t="s">
         <v>171</v>
       </c>
-      <c r="C75" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" t="s">
-        <v>172</v>
-      </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2684,13 +2678,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2698,16 +2692,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" t="s">
         <v>174</v>
       </c>
-      <c r="C77" t="s">
-        <v>19</v>
-      </c>
-      <c r="D77" t="s">
-        <v>175</v>
-      </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2715,13 +2709,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2729,19 +2723,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C79" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" t="s">
         <v>60</v>
       </c>
-      <c r="D79" t="s">
+      <c r="F79" t="s">
         <v>61</v>
       </c>
-      <c r="F79" t="s">
+      <c r="J79" t="s">
         <v>62</v>
-      </c>
-      <c r="J79" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2749,16 +2743,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" t="s">
         <v>64</v>
       </c>
-      <c r="C80" t="s">
-        <v>60</v>
-      </c>
-      <c r="D80" t="s">
-        <v>65</v>
-      </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2766,13 +2760,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2780,16 +2774,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" t="s">
         <v>178</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>179</v>
       </c>
-      <c r="D82" t="s">
-        <v>180</v>
-      </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2797,16 +2791,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>180</v>
+      </c>
+      <c r="C83" t="s">
+        <v>178</v>
+      </c>
+      <c r="D83" t="s">
         <v>181</v>
       </c>
-      <c r="C83" t="s">
-        <v>179</v>
-      </c>
-      <c r="D83" t="s">
-        <v>182</v>
-      </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -2814,13 +2808,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" t="s">
         <v>183</v>
       </c>
-      <c r="C84" t="s">
-        <v>184</v>
-      </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -2828,16 +2822,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" t="s">
+        <v>183</v>
+      </c>
+      <c r="D85" t="s">
         <v>185</v>
       </c>
-      <c r="C85" t="s">
-        <v>184</v>
-      </c>
-      <c r="D85" t="s">
-        <v>186</v>
-      </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2845,13 +2839,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" t="s">
         <v>187</v>
       </c>
-      <c r="C86" t="s">
-        <v>188</v>
-      </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2859,16 +2853,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>188</v>
+      </c>
+      <c r="C87" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" t="s">
         <v>189</v>
       </c>
-      <c r="C87" t="s">
-        <v>188</v>
-      </c>
-      <c r="D87" t="s">
-        <v>190</v>
-      </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2876,13 +2870,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2890,16 +2884,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>190</v>
+      </c>
+      <c r="C89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" t="s">
         <v>191</v>
       </c>
-      <c r="C89" t="s">
-        <v>188</v>
-      </c>
-      <c r="D89" t="s">
-        <v>192</v>
-      </c>
       <c r="F89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -2907,13 +2901,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -2921,16 +2915,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" t="s">
+        <v>127</v>
+      </c>
+      <c r="D91" t="s">
         <v>194</v>
       </c>
-      <c r="C91" t="s">
-        <v>128</v>
-      </c>
-      <c r="D91" t="s">
-        <v>195</v>
-      </c>
       <c r="F91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -2938,13 +2932,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C92" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -2952,19 +2946,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" t="s">
+        <v>158</v>
+      </c>
+      <c r="D93" t="s">
         <v>197</v>
       </c>
-      <c r="C93" t="s">
-        <v>159</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="F93" t="s">
+        <v>79</v>
+      </c>
+      <c r="K93" t="s">
         <v>198</v>
-      </c>
-      <c r="F93" t="s">
-        <v>80</v>
-      </c>
-      <c r="K93" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2972,16 +2966,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C94" t="s">
+        <v>158</v>
+      </c>
+      <c r="D94" t="s">
         <v>159</v>
       </c>
-      <c r="D94" t="s">
-        <v>160</v>
-      </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -2989,13 +2983,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C95" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3003,16 +2997,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -3020,13 +3014,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -3034,19 +3028,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E98" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3054,13 +3048,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -3068,16 +3062,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -3085,13 +3079,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -3099,19 +3093,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" t="s">
         <v>34</v>
-      </c>
-      <c r="F102" t="s">
-        <v>23</v>
-      </c>
-      <c r="K102" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,16 +3113,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" t="s">
         <v>36</v>
       </c>
-      <c r="C103" t="s">
-        <v>29</v>
-      </c>
-      <c r="D103" t="s">
-        <v>37</v>
-      </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -3136,13 +3130,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -3150,16 +3144,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -3167,13 +3161,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C106" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -3181,22 +3175,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" t="s">
         <v>211</v>
       </c>
-      <c r="C107" t="s">
-        <v>47</v>
-      </c>
-      <c r="D107" t="s">
-        <v>212</v>
-      </c>
       <c r="F107" t="s">
+        <v>40</v>
+      </c>
+      <c r="G107" t="s">
         <v>41</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>42</v>
-      </c>
-      <c r="H107" t="s">
-        <v>43</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
@@ -3207,16 +3201,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,13 +3218,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -3238,19 +3232,19 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" t="s">
         <v>215</v>
       </c>
-      <c r="C110" t="s">
-        <v>47</v>
-      </c>
-      <c r="D110" t="s">
-        <v>52</v>
-      </c>
-      <c r="E110" t="s">
-        <v>216</v>
-      </c>
       <c r="F110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -3258,13 +3252,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>216</v>
+      </c>
+      <c r="C111" t="s">
         <v>217</v>
       </c>
-      <c r="C111" t="s">
-        <v>218</v>
-      </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -3272,19 +3266,19 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>218</v>
+      </c>
+      <c r="C112" t="s">
+        <v>217</v>
+      </c>
+      <c r="D112" t="s">
         <v>219</v>
       </c>
-      <c r="C112" t="s">
-        <v>218</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
+        <v>79</v>
+      </c>
+      <c r="K112" t="s">
         <v>220</v>
-      </c>
-      <c r="F112" t="s">
-        <v>80</v>
-      </c>
-      <c r="K112" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -3292,19 +3286,19 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
+        <v>221</v>
+      </c>
+      <c r="C113" t="s">
+        <v>217</v>
+      </c>
+      <c r="D113" t="s">
         <v>222</v>
       </c>
-      <c r="C113" t="s">
-        <v>218</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="F113" t="s">
+        <v>79</v>
+      </c>
+      <c r="K113" t="s">
         <v>223</v>
-      </c>
-      <c r="F113" t="s">
-        <v>80</v>
-      </c>
-      <c r="K113" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -3312,16 +3306,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
+        <v>224</v>
+      </c>
+      <c r="C114" t="s">
+        <v>217</v>
+      </c>
+      <c r="D114" t="s">
         <v>225</v>
       </c>
-      <c r="C114" t="s">
-        <v>218</v>
-      </c>
-      <c r="D114" t="s">
-        <v>226</v>
-      </c>
       <c r="F114" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,13 +3323,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -3343,16 +3337,16 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F116" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -3360,13 +3354,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -3374,19 +3368,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K118" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3394,16 +3388,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C119" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -3411,13 +3405,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -3425,16 +3419,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>232</v>
+      </c>
+      <c r="C121" t="s">
+        <v>46</v>
+      </c>
+      <c r="D121" t="s">
         <v>233</v>
       </c>
-      <c r="C121" t="s">
-        <v>47</v>
-      </c>
-      <c r="D121" t="s">
-        <v>234</v>
-      </c>
       <c r="F121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -3442,13 +3436,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C122" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -3456,16 +3450,16 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
+        <v>235</v>
+      </c>
+      <c r="C123" t="s">
+        <v>46</v>
+      </c>
+      <c r="D123" t="s">
         <v>236</v>
       </c>
-      <c r="C123" t="s">
-        <v>47</v>
-      </c>
-      <c r="D123" t="s">
-        <v>237</v>
-      </c>
       <c r="F123" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -3473,22 +3467,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>237</v>
+      </c>
+      <c r="C124" t="s">
+        <v>46</v>
+      </c>
+      <c r="D124" t="s">
         <v>238</v>
       </c>
-      <c r="C124" t="s">
-        <v>47</v>
-      </c>
-      <c r="D124" t="s">
-        <v>239</v>
-      </c>
       <c r="F124" t="s">
+        <v>40</v>
+      </c>
+      <c r="G124" t="s">
         <v>41</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>42</v>
-      </c>
-      <c r="H124" t="s">
-        <v>43</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
@@ -3499,25 +3493,25 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>239</v>
+      </c>
+      <c r="C125" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" t="s">
         <v>240</v>
       </c>
-      <c r="C125" t="s">
-        <v>47</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="F125" t="s">
+        <v>40</v>
+      </c>
+      <c r="G125" t="s">
         <v>241</v>
       </c>
-      <c r="F125" t="s">
-        <v>41</v>
-      </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>242</v>
       </c>
-      <c r="H125" t="s">
-        <v>243</v>
-      </c>
       <c r="K125" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -3525,16 +3519,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>161</v>
+      </c>
+      <c r="C126" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" t="s">
         <v>162</v>
       </c>
-      <c r="C126" t="s">
-        <v>19</v>
-      </c>
-      <c r="D126" t="s">
-        <v>163</v>
-      </c>
       <c r="F126" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -3542,16 +3536,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" t="s">
         <v>164</v>
       </c>
-      <c r="C127" t="s">
-        <v>19</v>
-      </c>
-      <c r="D127" t="s">
-        <v>165</v>
-      </c>
       <c r="F127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -3559,10 +3553,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
+        <v>165</v>
+      </c>
+      <c r="F128" t="s">
         <v>166</v>
-      </c>
-      <c r="F128" t="s">
-        <v>167</v>
       </c>
       <c r="J128">
         <v>3</v>
@@ -3586,268 +3580,268 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" t="s">
         <v>248</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>249</v>
-      </c>
-      <c r="D2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" t="s">
         <v>251</v>
-      </c>
-      <c r="D3" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" t="s">
         <v>253</v>
-      </c>
-      <c r="D4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" t="s">
         <v>255</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>256</v>
-      </c>
-      <c r="D5" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" t="s">
         <v>258</v>
-      </c>
-      <c r="D6" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" t="s">
         <v>260</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>261</v>
-      </c>
-      <c r="D7" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D8" t="s">
         <v>263</v>
-      </c>
-      <c r="D8" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" t="s">
         <v>265</v>
-      </c>
-      <c r="D9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
         <v>267</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D11" t="s">
         <v>269</v>
-      </c>
-      <c r="D11" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" t="s">
         <v>271</v>
-      </c>
-      <c r="D12" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" t="s">
         <v>273</v>
-      </c>
-      <c r="D13" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" t="s">
         <v>275</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>276</v>
-      </c>
-      <c r="D14" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" t="s">
         <v>278</v>
-      </c>
-      <c r="D15" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
+        <v>280</v>
+      </c>
+      <c r="C17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" t="s">
         <v>281</v>
-      </c>
-      <c r="C17" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D18" t="s">
         <v>283</v>
-      </c>
-      <c r="D18" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" t="s">
         <v>285</v>
-      </c>
-      <c r="D19" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3866,71 +3860,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B9" s="2">
         <v>127</v>
@@ -3938,7 +3932,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B10" s="2">
         <v>20</v>
@@ -3946,7 +3940,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B11" s="2">
         <v>56</v>
@@ -3954,15 +3948,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B13" s="3">
         <v>46146</v>
@@ -3970,7 +3964,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B14" s="3">
         <v>46146</v>
@@ -3978,31 +3972,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -4010,18 +4004,18 @@
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -4040,214 +4034,220 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\TaskMgmt_FloorPlan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9AEA2-C4D4-4D34-B55C-67182E3B47E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E68CA31-7A27-4D1A-BE21-47C7AE70A2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{C0C90F87-48CD-475A-8923-C466A25A0B95}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="321">
   <si>
     <t>StepNo</t>
   </si>
@@ -999,6 +999,9 @@
   </si>
   <si>
     <t>Key</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1838,7 @@
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1926,7 +1929,7 @@
         <v>82</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/TaskMgmt_FloorPlan/LSTP_TaskMgmt_FloorPlan_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\TaskMgmt_FloorPlan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E68CA31-7A27-4D1A-BE21-47C7AE70A2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7B2197-C81A-4F06-B874-06DEFF53F5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{C0C90F87-48CD-475A-8923-C466A25A0B95}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="324">
   <si>
     <t>StepNo</t>
   </si>
@@ -392,9 +392,6 @@
     <t>Select Intended Management</t>
   </si>
   <si>
-    <t>cmb_intended management</t>
-  </si>
-  <si>
     <t>INTENDED_MANAGEMENT</t>
   </si>
   <si>
@@ -476,9 +473,6 @@
     <t>Click task recipients icon to select User B</t>
   </si>
   <si>
-    <t>icn_task recipients</t>
-  </si>
-  <si>
     <t>Wait for user search form</t>
   </si>
   <si>
@@ -716,9 +710,6 @@
     <t>Click Finish Now to complete transfer</t>
   </si>
   <si>
-    <t>btn_Finish nowCP</t>
-  </si>
-  <si>
     <t>Wait for transfer confirmation</t>
   </si>
   <si>
@@ -1002,6 +993,24 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>pageDefUsers</t>
+  </si>
+  <si>
+    <t>pagePatientSearchResult</t>
+  </si>
+  <si>
+    <t>pagePbrdHistory</t>
+  </si>
+  <si>
+    <t>cmb_intendedManagement</t>
+  </si>
+  <si>
+    <t>icn_taskRecipients</t>
+  </si>
+  <si>
+    <t>btn_FinishNowCP</t>
   </si>
 </sst>
 </file>
@@ -1838,7 +1847,7 @@
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1929,7 +1938,7 @@
         <v>82</v>
       </c>
       <c r="F30" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2204,13 +2213,13 @@
         <v>109</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>321</v>
       </c>
       <c r="F46" t="s">
         <v>79</v>
       </c>
       <c r="K46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2218,13 +2227,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
         <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F47" t="s">
         <v>22</v>
@@ -2235,7 +2244,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C48" t="s">
         <v>109</v>
@@ -2249,7 +2258,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -2266,7 +2275,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -2280,13 +2289,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
@@ -2297,10 +2306,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" t="s">
         <v>126</v>
-      </c>
-      <c r="C52" t="s">
-        <v>127</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -2311,13 +2320,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
         <v>128</v>
-      </c>
-      <c r="C53" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" t="s">
-        <v>129</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
@@ -2328,10 +2337,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -2342,13 +2351,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55" t="s">
         <v>131</v>
-      </c>
-      <c r="C55" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" t="s">
-        <v>132</v>
       </c>
       <c r="F55" t="s">
         <v>22</v>
@@ -2359,13 +2368,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" t="s">
         <v>134</v>
-      </c>
-      <c r="D56" t="s">
-        <v>135</v>
       </c>
       <c r="F56" t="s">
         <v>22</v>
@@ -2376,10 +2385,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s">
         <v>19</v>
@@ -2390,19 +2399,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" t="s">
         <v>137</v>
-      </c>
-      <c r="C58" t="s">
-        <v>134</v>
-      </c>
-      <c r="D58" t="s">
-        <v>138</v>
       </c>
       <c r="F58" t="s">
         <v>79</v>
       </c>
       <c r="K58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2410,13 +2419,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
         <v>109</v>
       </c>
       <c r="D59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
@@ -2427,10 +2436,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" t="s">
         <v>142</v>
-      </c>
-      <c r="C60" t="s">
-        <v>143</v>
       </c>
       <c r="F60" t="s">
         <v>19</v>
@@ -2441,13 +2450,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="F61" t="s">
         <v>22</v>
@@ -2458,10 +2467,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F62" t="s">
         <v>19</v>
@@ -2472,19 +2481,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C63" t="s">
+        <v>318</v>
+      </c>
+      <c r="D63" t="s">
         <v>147</v>
-      </c>
-      <c r="D63" t="s">
-        <v>149</v>
       </c>
       <c r="F63" t="s">
         <v>61</v>
       </c>
       <c r="K63" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2492,13 +2501,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F64" t="s">
         <v>22</v>
@@ -2509,10 +2518,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F65" t="s">
         <v>19</v>
@@ -2523,13 +2532,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="D66" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F66" t="s">
         <v>22</v>
@@ -2540,10 +2549,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F67" t="s">
         <v>19</v>
@@ -2554,13 +2563,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" t="s">
         <v>157</v>
-      </c>
-      <c r="C68" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" t="s">
-        <v>159</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
@@ -2571,10 +2580,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -2585,13 +2594,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
         <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -2602,13 +2611,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F71" t="s">
         <v>22</v>
@@ -2619,10 +2628,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F72" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -2633,7 +2642,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -2642,7 +2651,7 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2650,7 +2659,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -2664,13 +2673,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F75" t="s">
         <v>22</v>
@@ -2681,7 +2690,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -2695,13 +2704,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F77" t="s">
         <v>22</v>
@@ -2712,7 +2721,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
         <v>59</v>
@@ -2726,7 +2735,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
         <v>59</v>
@@ -2777,13 +2786,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" t="s">
         <v>177</v>
-      </c>
-      <c r="C82" t="s">
-        <v>178</v>
-      </c>
-      <c r="D82" t="s">
-        <v>179</v>
       </c>
       <c r="F82" t="s">
         <v>22</v>
@@ -2794,13 +2803,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="D83" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F83" t="s">
         <v>22</v>
@@ -2811,10 +2820,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s">
         <v>19</v>
@@ -2825,13 +2834,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" t="s">
         <v>183</v>
-      </c>
-      <c r="D85" t="s">
-        <v>185</v>
       </c>
       <c r="F85" t="s">
         <v>22</v>
@@ -2842,10 +2851,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F86" t="s">
         <v>19</v>
@@ -2856,13 +2865,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
+        <v>185</v>
+      </c>
+      <c r="D87" t="s">
         <v>187</v>
-      </c>
-      <c r="D87" t="s">
-        <v>189</v>
       </c>
       <c r="F87" t="s">
         <v>22</v>
@@ -2873,10 +2882,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C88" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F88" t="s">
         <v>19</v>
@@ -2887,13 +2896,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C89" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D89" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F89" t="s">
         <v>22</v>
@@ -2904,10 +2913,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C90" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2918,13 +2927,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F91" t="s">
         <v>22</v>
@@ -2935,10 +2944,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C92" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -2949,19 +2958,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F93" t="s">
         <v>79</v>
       </c>
       <c r="K93" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -2969,13 +2978,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C94" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D94" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
@@ -2986,10 +2995,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C95" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3000,7 +3009,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
@@ -3017,7 +3026,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
@@ -3031,7 +3040,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
         <v>28</v>
@@ -3051,7 +3060,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C99" t="s">
         <v>28</v>
@@ -3065,7 +3074,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C100" t="s">
         <v>28</v>
@@ -3082,7 +3091,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C101" t="s">
         <v>28</v>
@@ -3096,7 +3105,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C102" t="s">
         <v>28</v>
@@ -3133,7 +3142,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C104" t="s">
         <v>28</v>
@@ -3147,7 +3156,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C105" t="s">
         <v>28</v>
@@ -3164,7 +3173,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C106" t="s">
         <v>46</v>
@@ -3178,13 +3187,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C107" t="s">
         <v>46</v>
       </c>
       <c r="D107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F107" t="s">
         <v>40</v>
@@ -3204,13 +3213,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C108" t="s">
         <v>46</v>
       </c>
       <c r="D108" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F108" t="s">
         <v>22</v>
@@ -3221,7 +3230,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C109" t="s">
         <v>46</v>
@@ -3235,7 +3244,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C110" t="s">
         <v>46</v>
@@ -3244,7 +3253,7 @@
         <v>51</v>
       </c>
       <c r="E110" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F110" t="s">
         <v>22</v>
@@ -3255,10 +3264,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C111" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F111" t="s">
         <v>19</v>
@@ -3269,19 +3278,19 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C112" t="s">
+        <v>215</v>
+      </c>
+      <c r="D112" t="s">
         <v>217</v>
-      </c>
-      <c r="D112" t="s">
-        <v>219</v>
       </c>
       <c r="F112" t="s">
         <v>79</v>
       </c>
       <c r="K112" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -3289,19 +3298,19 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D113" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F113" t="s">
         <v>79</v>
       </c>
       <c r="K113" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -3309,13 +3318,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C114" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
       <c r="F114" t="s">
         <v>22</v>
@@ -3326,10 +3335,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F115" t="s">
         <v>19</v>
@@ -3340,7 +3349,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C116" t="s">
         <v>28</v>
@@ -3357,7 +3366,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
         <v>28</v>
@@ -3371,7 +3380,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C118" t="s">
         <v>28</v>
@@ -3383,7 +3392,7 @@
         <v>22</v>
       </c>
       <c r="K118" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3391,7 +3400,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C119" t="s">
         <v>28</v>
@@ -3408,7 +3417,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C120" t="s">
         <v>28</v>
@@ -3422,13 +3431,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C121" t="s">
         <v>46</v>
       </c>
       <c r="D121" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F121" t="s">
         <v>22</v>
@@ -3439,7 +3448,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C122" t="s">
         <v>46</v>
@@ -3453,13 +3462,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C123" t="s">
         <v>46</v>
       </c>
       <c r="D123" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -3470,13 +3479,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C124" t="s">
-        <v>46</v>
+        <v>320</v>
       </c>
       <c r="D124" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F124" t="s">
         <v>40</v>
@@ -3496,25 +3505,25 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C125" t="s">
-        <v>46</v>
+        <v>320</v>
       </c>
       <c r="D125" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F125" t="s">
         <v>40</v>
       </c>
       <c r="G125" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H125" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K125" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -3522,13 +3531,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -3539,13 +3548,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F127" t="s">
         <v>22</v>
@@ -3556,10 +3565,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F128" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J128">
         <v>3</v>
@@ -3583,16 +3592,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3600,41 +3609,41 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
         <v>247</v>
       </c>
-      <c r="C3" t="s">
-        <v>250</v>
-      </c>
       <c r="D3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3642,27 +3651,27 @@
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" t="s">
         <v>254</v>
       </c>
-      <c r="C6" t="s">
-        <v>257</v>
-      </c>
       <c r="D6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3670,13 +3679,13 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3684,13 +3693,13 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" t="s">
         <v>259</v>
       </c>
-      <c r="C8" t="s">
-        <v>262</v>
-      </c>
       <c r="D8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3698,13 +3707,13 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3712,13 +3721,13 @@
         <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3726,13 +3735,13 @@
         <v>94</v>
       </c>
       <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" t="s">
         <v>266</v>
-      </c>
-      <c r="C11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D11" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3740,13 +3749,13 @@
         <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3754,13 +3763,13 @@
         <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3768,13 +3777,13 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3782,69 +3791,69 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C15" t="s">
         <v>274</v>
       </c>
-      <c r="C15" t="s">
-        <v>277</v>
-      </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" t="s">
         <v>280</v>
-      </c>
-      <c r="C18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D18" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D19" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3863,71 +3872,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B9" s="2">
         <v>127</v>
@@ -3935,7 +3944,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B10" s="2">
         <v>20</v>
@@ -3943,7 +3952,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B11" s="2">
         <v>56</v>
@@ -3951,15 +3960,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B13" s="3">
         <v>46146</v>
@@ -3967,7 +3976,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B14" s="3">
         <v>46146</v>
@@ -3975,31 +3984,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -4007,18 +4016,18 @@
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4037,13 +4046,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,32 +4060,32 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4084,21 +4093,21 @@
         <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4106,10 +4115,10 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4117,10 +4126,10 @@
         <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4128,10 +4137,10 @@
         <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4150,10 +4159,10 @@
         <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4161,10 +4170,10 @@
         <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4172,10 +4181,10 @@
         <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4183,10 +4192,10 @@
         <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,15 +4203,15 @@
         <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -4213,35 +4222,35 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
